--- a/reports/Debug-snowbowl-20260106/Week Total (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-snowbowl-20260106/Week Total (Prior Year)_Revenue.xlsx
@@ -61,10 +61,10 @@
     <t>T101</t>
   </si>
   <si>
+    <t>T257</t>
+  </si>
+  <si>
     <t>T121</t>
-  </si>
-  <si>
-    <t>T257</t>
   </si>
   <si>
     <t>T103</t>
@@ -543,7 +543,7 @@
         <v>19</v>
       </c>
       <c r="D5" s="2">
-        <v>9226.19</v>
+        <v>21.38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -557,7 +557,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="2">
-        <v>21.38</v>
+        <v>9226.19</v>
       </c>
     </row>
     <row r="7" spans="1:4">
